--- a/tests/test_data/test_expense_report.xlsx
+++ b/tests/test_data/test_expense_report.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29311"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3F731F8A-5C92-42AA-B2F9-CBDAE75419AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/quyvu/code/ez-expense/tests/test_data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49B0A75C-4184-6648-BED3-44F92EF06F9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="28300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="30">
   <si>
     <t>Payment method</t>
   </si>
@@ -115,13 +120,19 @@
   </si>
   <si>
     <t>25.57 GBP</t>
+  </si>
+  <si>
+    <t>Hotel</t>
+  </si>
+  <si>
+    <t>1369.35 USD</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -203,9 +214,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -243,7 +254,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -349,7 +360,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -491,7 +502,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -525,10 +536,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I12"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18" style="1"/>
-    <col min="2" max="2" width="8" style="2"/>
+    <col min="2" max="2" width="10.5" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20" style="1"/>
     <col min="4" max="4" width="12" style="1"/>
     <col min="5" max="5" width="10" style="3"/>
@@ -538,7 +549,7 @@
     <col min="9" max="9" width="14" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -567,7 +578,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
@@ -596,24 +607,24 @@
         <v>5837209576</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B3" s="2">
-        <v>45910</v>
+        <v>46184</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="F3" s="4">
-        <v>9.31</v>
+        <v>1000</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>15</v>
@@ -625,7 +636,7 @@
         <v>5837361585</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>17</v>
       </c>
@@ -651,7 +662,7 @@
         <v>5837529393</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>17</v>
       </c>
@@ -659,7 +670,7 @@
         <v>45910</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>19</v>
@@ -677,7 +688,7 @@
         <v>5837680359</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>17</v>
       </c>
@@ -703,7 +714,7 @@
         <v>5838470605</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>17</v>
       </c>
@@ -729,7 +740,7 @@
         <v>5838706201</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>17</v>
       </c>
@@ -755,7 +766,7 @@
         <v>5838696567</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>17</v>
       </c>
@@ -781,7 +792,7 @@
         <v>5839120223</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>17</v>
       </c>
@@ -807,7 +818,7 @@
         <v>5839120224</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>17</v>
       </c>
@@ -833,7 +844,7 @@
         <v>5839307127</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>17</v>
       </c>
@@ -865,4 +876,10 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{f42aa342-8706-4288-bd11-ebb85995028c}" enabled="1" method="Standard" siteId="{72f988bf-86f1-41af-91ab-2d7cd011db47}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>